--- a/output/pdf_financials_xlsx/APL.xlsx
+++ b/output/pdf_financials_xlsx/APL.xlsx
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.070808</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>0.334345</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.688417</v>
+        <v>1.617609</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-0.144544</v>
@@ -2207,7 +2207,7 @@
         <v>0.334345</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.688417</v>
+        <v>1.617609</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-0.144544</v>
@@ -2429,34 +2429,34 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.021314</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.098124</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.045477</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.07292899999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.080668</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.01332</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.127375</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.013505</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.173195</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.374432</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.339473</v>
@@ -2553,34 +2553,34 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.021314</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.098124</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.045477</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.07292899999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.080668</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.01332</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.127375</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.013505</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.173195</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.374432</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.339473</v>
@@ -3297,34 +3297,34 @@
         <v>0.918831</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.071216</v>
+        <v>0.049902</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.148067</v>
+        <v>0.049943</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.105369</v>
+        <v>0.059892</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.17653</v>
+        <v>0.103601</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.14076</v>
+        <v>0.060092</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.09023299999999999</v>
+        <v>0.076913</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.189674</v>
+        <v>0.062299</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.07799300000000001</v>
+        <v>0.064488</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.236575</v>
+        <v>0.06338000000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.433595</v>
+        <v>0.059163</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.064163</v>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -40287,7 +40287,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -41101,7 +41101,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">

--- a/output/pdf_financials_xlsx/APL.xlsx
+++ b/output/pdf_financials_xlsx/APL.xlsx
@@ -7193,46 +7193,46 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.012278</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.004339</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.00958</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.016854</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.007373</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.038611</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.000209</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.038328</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.004487</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.036816</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.005398</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.053578</v>
       </c>
       <c r="N112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.018476</v>
       </c>
       <c r="P112" s="3" t="n">
         <v>0</v>
@@ -27777,7 +27777,11 @@
           <t>Proceeds from disposal of property and equipment 7</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -29216,7 +29220,11 @@
           <t>Proceeds from disposal of property and equipment .…</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -30394,7 +30402,11 @@
           <t>Proceeds from disposal of property and equipment 7.…</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -33572,7 +33584,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -37996,7 +38012,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E297" s="5" t="n">
         <v>0.012278</v>
       </c>
@@ -38596,7 +38616,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E303" s="5" t="n">
         <v>0.003547</v>
       </c>
